--- a/public/examples/ЕКБ ВБ ОТ 1.06 (КОРОБА ДО 25 КГ).xlsx
+++ b/public/examples/ЕКБ ВБ ОТ 1.06 (КОРОБА ДО 25 КГ).xlsx
@@ -1417,53 +1417,73 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
